--- a/artfynd/A 9166-2022 artfynd.xlsx
+++ b/artfynd/A 9166-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9166-2022 artfynd.xlsx
+++ b/artfynd/A 9166-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99132386</v>
+        <v>99132391</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>341186.9221080806</v>
+        <v>340560</v>
       </c>
       <c r="R2" t="n">
-        <v>6555962.760956436</v>
+        <v>6555830</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -775,6 +760,11 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>barrnaturskog med talldominans</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99132406</v>
+        <v>99132415</v>
       </c>
       <c r="B3" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>341234.6652704263</v>
+        <v>341543</v>
       </c>
       <c r="R3" t="n">
-        <v>6556120.142994496</v>
+        <v>6556285</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,21 +850,11 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +866,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>barrnaturskog med talldominans</t>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99132411</v>
+        <v>99132416</v>
       </c>
       <c r="B4" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>341365.5803920132</v>
+        <v>341548</v>
       </c>
       <c r="R4" t="n">
-        <v>6556159.941453976</v>
+        <v>6556256</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,26 +957,11 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>gamla gnagspår</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1013,12 +973,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>barrnaturskog med talldominans</t>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>torrtall</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1039,12 +999,7 @@
         <v>99132420</v>
       </c>
       <c r="B5" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>341603.2791425092</v>
+        <v>341603</v>
       </c>
       <c r="R5" t="n">
-        <v>6556253.915939005</v>
+        <v>6556254</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,19 +1064,9 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,53 +1103,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99132383</v>
+        <v>99907131</v>
       </c>
       <c r="B6" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sydväst Storetjärnet, Dls</t>
+          <t>Låga, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>341277.8554730046</v>
+        <v>341234</v>
       </c>
       <c r="R6" t="n">
-        <v>6555969.777043636</v>
+        <v>6555970</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,22 +1172,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Observerad under Naturskyddsföreningens signalartskurs</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,43 +1191,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>barrnaturskog med talldominans</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Robin Karlsson, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99132391</v>
+        <v>99907797</v>
       </c>
       <c r="B7" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,19 +1239,23 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sydväst Storetjärnet, Dls</t>
+          <t>Låga, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340559.737086219</v>
+        <v>341552</v>
       </c>
       <c r="R7" t="n">
-        <v>6555829.515892345</v>
+        <v>6556233</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1350,22 +1279,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Observerad under Naturskyddsföreningens signalartskurs</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,43 +1298,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>barrnaturskog med talldominans</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>tallåga</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Robin Karlsson, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99132389</v>
+        <v>99132404</v>
       </c>
       <c r="B8" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1442,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>340910.2715792965</v>
+        <v>341144</v>
       </c>
       <c r="R8" t="n">
-        <v>6555849.345858485</v>
+        <v>6556066</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1475,21 +1385,11 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1506,7 +1406,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>gammeltall</t>
+          <t>torraka</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1524,15 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>99132394</v>
+        <v>99132384</v>
       </c>
       <c r="B9" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1564,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>340826.2260859018</v>
+        <v>341213</v>
       </c>
       <c r="R9" t="n">
-        <v>6555933.562909372</v>
+        <v>6555991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,26 +1492,11 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>gamla gnagspår</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1629,11 +1509,6 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>barrnaturskog med talldominans</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>torrtall</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1651,15 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>99132396</v>
+        <v>99132387</v>
       </c>
       <c r="B10" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>340879.9498507975</v>
+        <v>341163</v>
       </c>
       <c r="R10" t="n">
-        <v>6555962.170636989</v>
+        <v>6555950</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1724,19 +1594,9 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1768,15 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>99132398</v>
+        <v>99132388</v>
       </c>
       <c r="B11" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1784,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1808,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341080.8537766242</v>
+        <v>341071</v>
       </c>
       <c r="R11" t="n">
-        <v>6556037.603631846</v>
+        <v>6555936</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,19 +1696,9 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1885,15 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>99132409</v>
+        <v>99132390</v>
       </c>
       <c r="B12" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1901,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1925,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341328.8048794235</v>
+        <v>340549</v>
       </c>
       <c r="R12" t="n">
-        <v>6556142.448534912</v>
+        <v>6555814</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1958,26 +1798,11 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>gamla gnagspår</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1990,11 +1815,6 @@
       <c r="AI12" t="inlineStr">
         <is>
           <t>barrnaturskog med talldominans</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>torrtall</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2012,15 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>99132418</v>
+        <v>99132393</v>
       </c>
       <c r="B13" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2052,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341586.0590043708</v>
+        <v>340742</v>
       </c>
       <c r="R13" t="n">
-        <v>6556248.461543149</v>
+        <v>6555893</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2085,21 +1900,11 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2111,12 +1916,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>granlåga</t>
+          <t>barrnaturskog med talldominans</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2134,37 +1934,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>99132416</v>
+        <v>99132396</v>
       </c>
       <c r="B14" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2174,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341548.2723863912</v>
+        <v>340880</v>
       </c>
       <c r="R14" t="n">
-        <v>6556256.197766491</v>
+        <v>6555962</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2207,21 +2002,11 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2233,12 +2018,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>tallåga</t>
+          <t>barrnaturskog med talldominans</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2256,15 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>99132405</v>
+        <v>99132402</v>
       </c>
       <c r="B15" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341232.0755286817</v>
+        <v>341117</v>
       </c>
       <c r="R15" t="n">
-        <v>6556107.398725042</v>
+        <v>6556059</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2329,19 +2104,9 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2373,37 +2138,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>99132395</v>
+        <v>99132405</v>
       </c>
       <c r="B16" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2413,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>340848.3967964154</v>
+        <v>341232</v>
       </c>
       <c r="R16" t="n">
-        <v>6555946.519873871</v>
+        <v>6556107</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2446,21 +2206,11 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2473,11 +2223,6 @@
       <c r="AI16" t="inlineStr">
         <is>
           <t>barrnaturskog med talldominans</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>gammeltall</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2495,37 +2240,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>99132382</v>
+        <v>99132406</v>
       </c>
       <c r="B17" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2535,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>341335.2828762638</v>
+        <v>341235</v>
       </c>
       <c r="R17" t="n">
-        <v>6555988.468844471</v>
+        <v>6556120</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2568,21 +2308,11 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2595,11 +2325,6 @@
       <c r="AI17" t="inlineStr">
         <is>
           <t>barrnaturskog med talldominans</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>gammeltall</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2617,15 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>99132388</v>
+        <v>99906701</v>
       </c>
       <c r="B18" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2653,14 +2373,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sydväst Storetjärnet, Dls</t>
+          <t>Tallhed, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>341071.4630821242</v>
+        <v>341172</v>
       </c>
       <c r="R18" t="n">
-        <v>6555935.68925692</v>
+        <v>6556080</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2687,22 +2407,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Observerad under Naturskyddsföreningens signalartskurs</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2713,36 +2428,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>barrnaturskog med talldominans</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>99132387</v>
+        <v>99907368</v>
       </c>
       <c r="B19" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2768,19 +2473,23 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sydväst Storetjärnet, Dls</t>
+          <t>Tallskog, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>341163.2317166748</v>
+        <v>341164</v>
       </c>
       <c r="R19" t="n">
-        <v>6555950.379509101</v>
+        <v>6556090</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2804,22 +2513,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Observerad under Naturskyddsföreningens signalartskurs</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2828,38 +2532,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>barrnaturskog med talldominans</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Robin Karlsson, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>99132393</v>
+        <v>100855557</v>
       </c>
       <c r="B20" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,17 +2582,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sydväst Storetjärnet, Dls</t>
+          <t>Kråkviken, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>340742.1469427192</v>
+        <v>341118</v>
       </c>
       <c r="R20" t="n">
-        <v>6555893.368408962</v>
+        <v>6555905</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2921,22 +2616,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2947,36 +2632,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>barrnaturskog med talldominans</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>99132384</v>
+        <v>100855567</v>
       </c>
       <c r="B21" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3004,17 +2679,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sydväst Storetjärnet, Dls</t>
+          <t>Kråkviken, Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>341213.330234039</v>
+        <v>341160</v>
       </c>
       <c r="R21" t="n">
-        <v>6555990.966445948</v>
+        <v>6556102</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3038,22 +2713,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3064,36 +2729,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>barrnaturskog med talldominans</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>99132401</v>
+        <v>101910138</v>
       </c>
       <c r="B22" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3101,37 +2756,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sydväst Storetjärnet, Dls</t>
+          <t>Bengtsfors, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>341106.8138842176</v>
+        <v>341195</v>
       </c>
       <c r="R22" t="n">
-        <v>6556055.0307057</v>
+        <v>6555916</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3155,22 +2812,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2022-06-27</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2022-06-27</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3181,36 +2838,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>barrnaturskog med talldominans</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>99132404</v>
+        <v>99132386</v>
       </c>
       <c r="B23" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3218,21 +2865,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3242,10 +2889,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>341144.3634203465</v>
+        <v>341187</v>
       </c>
       <c r="R23" t="n">
-        <v>6556066.320872108</v>
+        <v>6555963</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3275,21 +2922,11 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3302,11 +2939,6 @@
       <c r="AI23" t="inlineStr">
         <is>
           <t>barrnaturskog med talldominans</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>torraka</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3324,37 +2956,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>99132402</v>
+        <v>99132398</v>
       </c>
       <c r="B24" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3364,10 +2991,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>341116.7527608229</v>
+        <v>341081</v>
       </c>
       <c r="R24" t="n">
-        <v>6556058.729926346</v>
+        <v>6556038</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3397,19 +3024,9 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3441,15 +3058,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>99906700</v>
+        <v>99132401</v>
       </c>
       <c r="B25" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3457,40 +3069,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Silvertall, Dls</t>
+          <t>Sydväst Storetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>341144.7921475561</v>
+        <v>341107</v>
       </c>
       <c r="R25" t="n">
-        <v>6556064.246701518</v>
+        <v>6556055</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3514,27 +3123,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Observerad under Naturskyddsföreningens signalartskurs. Upptäckare Ingvar 2 som såg något intressant på samma silvertall som ärgspiken.</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3543,75 +3137,71 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>barrnaturskog med talldominans</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Robin Karlsson, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>99906692</v>
+        <v>100855568</v>
       </c>
       <c r="B26" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6428</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Blöt remsa, Dls</t>
+          <t>Kråkviken, Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>341353.6632309288</v>
+        <v>341169</v>
       </c>
       <c r="R26" t="n">
-        <v>6555984.620782993</v>
+        <v>6556125</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3635,27 +3225,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Observerad under Naturskyddsföreningens signalartskurs</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3664,69 +3239,63 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>99906701</v>
+        <v>99132382</v>
       </c>
       <c r="B27" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tallhed, Dls</t>
+          <t>Sydväst Storetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>341172.2087173784</v>
+        <v>341335</v>
       </c>
       <c r="R27" t="n">
-        <v>6556079.557143834</v>
+        <v>6555988</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3753,27 +3322,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Observerad under Naturskyddsföreningens signalartskurs</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3784,31 +3338,36 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>barrnaturskog med talldominans</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>gammeltall</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>99907797</v>
+        <v>99132389</v>
       </c>
       <c r="B28" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3816,41 +3375,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Låga, Dls</t>
+          <t>Sydväst Storetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>341552.4551206058</v>
+        <v>340910</v>
       </c>
       <c r="R28" t="n">
-        <v>6556232.891735436</v>
+        <v>6555849</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3874,27 +3429,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Observerad under Naturskyddsföreningens signalartskurs</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3903,76 +3443,76 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>barrnaturskog med talldominans</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>gammeltall</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Robin Karlsson, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>99907368</v>
+        <v>99132395</v>
       </c>
       <c r="B29" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tallskog, Dls</t>
+          <t>Sydväst Storetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>341164.3885279179</v>
+        <v>340848</v>
       </c>
       <c r="R29" t="n">
-        <v>6556089.649914237</v>
+        <v>6555947</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3996,27 +3536,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Observerad under Naturskyddsföreningens signalartskurs</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4025,19 +3550,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>barrnaturskog med talldominans</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>gammeltall</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Robin Karlsson, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4047,12 +3581,7 @@
         <v>99957040</v>
       </c>
       <c r="B30" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4099,10 +3628,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>341038.3563264356</v>
+        <v>341038</v>
       </c>
       <c r="R30" t="n">
-        <v>6556018.808509341</v>
+        <v>6556019</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4197,15 +3726,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>99907131</v>
+        <v>100855558</v>
       </c>
       <c r="B31" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4213,41 +3737,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Låga, Dls</t>
+          <t>Kråkviken, Dls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>341233.5557554136</v>
+        <v>340912</v>
       </c>
       <c r="R31" t="n">
-        <v>6555969.561854991</v>
+        <v>6555864</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4271,27 +3791,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Observerad under Naturskyddsföreningens signalartskurs</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4300,34 +3805,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Robin Karlsson, Sebastian Kirppu</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>100855561</v>
+        <v>101909725</v>
       </c>
       <c r="B32" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4335,42 +3834,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kråkviken, Dls</t>
+          <t>Bengtsfors, Dls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>340780.9940205512</v>
+        <v>341334</v>
       </c>
       <c r="R32" t="n">
-        <v>6555738.02611561</v>
+        <v>6555988</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4394,22 +3893,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
+          <t>2022-06-27</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
+          <t>2022-06-27</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4424,27 +3923,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>100855566</v>
+        <v>99132383</v>
       </c>
       <c r="B33" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4452,46 +3946,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kråkviken, Dls</t>
+          <t>Sydväst Storetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>341098.8016433357</v>
+        <v>341278</v>
       </c>
       <c r="R33" t="n">
-        <v>6556060.504905555</v>
+        <v>6555970</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4515,22 +4000,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4539,49 +4014,38 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>barrnaturskog med talldominans</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>100855567</v>
+        <v>99132418</v>
       </c>
       <c r="B34" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4589,37 +4053,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2180</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kråkviken, Dls</t>
+          <t>Sydväst Storetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>341160.2524783426</v>
+        <v>341586</v>
       </c>
       <c r="R34" t="n">
-        <v>6556101.645775153</v>
+        <v>6556248</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4643,22 +4107,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4669,16 +4123,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4688,12 +4152,7 @@
         <v>100855577</v>
       </c>
       <c r="B35" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4725,10 +4184,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>341584.1303929769</v>
+        <v>341584</v>
       </c>
       <c r="R35" t="n">
-        <v>6556251.625867508</v>
+        <v>6556252</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4758,19 +4217,9 @@
           <t>2022-05-12</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4812,53 +4261,51 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>100855558</v>
+        <v>99906692</v>
       </c>
       <c r="B36" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>6428</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kråkviken, Dls</t>
+          <t>Blöt remsa, Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>340912.4125228857</v>
+        <v>341353</v>
       </c>
       <c r="R36" t="n">
-        <v>6555863.65192385</v>
+        <v>6555985</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4882,22 +4329,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Observerad under Naturskyddsföreningens signalartskurs</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4906,33 +4348,29 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>100855575</v>
+        <v>99906700</v>
       </c>
       <c r="B37" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4940,39 +4378,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kråkviken, Dls</t>
+          <t>Silvertall, Dls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>341522.2974847538</v>
+        <v>341145</v>
       </c>
       <c r="R37" t="n">
-        <v>6556225.918125159</v>
+        <v>6556065</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4999,22 +4435,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Observerad under Naturskyddsföreningens signalartskurs. Upptäckare Ingvar 2 som såg något intressant på samma silvertall som ärgspiken.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5023,33 +4454,29 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Robin Karlsson, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>100855557</v>
+        <v>100855561</v>
       </c>
       <c r="B38" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5057,34 +4484,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kråkviken, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>341118.5954102003</v>
+        <v>340780</v>
       </c>
       <c r="R38" t="n">
-        <v>6555904.938522851</v>
+        <v>6555738</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5114,19 +4546,9 @@
           <t>2022-05-12</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5153,58 +4575,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>101909725</v>
+        <v>100855575</v>
       </c>
       <c r="B39" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bengtsfors, Dls</t>
+          <t>Kråkviken, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>341334.2120006271</v>
+        <v>341523</v>
       </c>
       <c r="R39" t="n">
-        <v>6555987.485145619</v>
+        <v>6556226</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5228,22 +4645,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-06-27</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-06-27</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5258,27 +4665,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>101910138</v>
+        <v>98776597</v>
       </c>
       <c r="B40" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5286,36 +4688,45 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bengtsfors, Dls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>341195.2841222521</v>
+        <v>341549</v>
       </c>
       <c r="R40" t="n">
-        <v>6555916.144197992</v>
+        <v>6556266</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5342,22 +4753,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-06-27</t>
+          <t>2022-02-26</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-06-27</t>
+          <t>2022-02-26</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5384,15 +4795,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>99677166</v>
+        <v>98985886</v>
       </c>
       <c r="B41" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5400,44 +4806,48 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bengtsfors, Dls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>341246.7052525753</v>
+        <v>341207</v>
       </c>
       <c r="R41" t="n">
-        <v>6555988.550884079</v>
+        <v>6556094</v>
       </c>
       <c r="S41" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5461,22 +4871,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2022-03-25</t>
+          <t>2022-03-08</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2022-03-25</t>
+          <t>2022-03-08</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5491,15 +4901,709 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>99677166</v>
+      </c>
+      <c r="B42" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Bengtsfors, Dls</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>341246</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6555989</v>
+      </c>
+      <c r="S42" t="n">
+        <v>46</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2022-03-25</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2022-03-25</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
           <t>Mayra Caldiz</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
+      <c r="AX42" t="inlineStr">
         <is>
           <t>Mayra Caldiz</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>99132394</v>
+      </c>
+      <c r="B43" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Sydväst Storetjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>340826</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6555934</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2022-03-12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2022-03-12</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>gamla gnagspår</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>barrnaturskog med talldominans</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>torrtall</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>99132409</v>
+      </c>
+      <c r="B44" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sydväst Storetjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>341329</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6556142</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2022-03-12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2022-03-12</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>gamla gnagspår</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>barrnaturskog med talldominans</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>torrtall</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>99132411</v>
+      </c>
+      <c r="B45" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sydväst Storetjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>341366</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6556160</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2022-03-12</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2022-03-12</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>gamla gnagspår</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>barrnaturskog med talldominans</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>torrtall</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>100855566</v>
+      </c>
+      <c r="B46" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kråkviken, Dls</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>341098</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6556061</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2022-05-12</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2022-05-12</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>100855573</v>
+      </c>
+      <c r="B47" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kråkviken, Dls</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>341378</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6556210</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2022-05-12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2022-05-12</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9166-2022 artfynd.xlsx
+++ b/artfynd/A 9166-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132391</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132415</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132416</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132420</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99907131</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99907797</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132404</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132384</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132387</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1727,6 +1777,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132388</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132390</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1931,6 +1991,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132393</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2033,6 +2098,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132396</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2135,6 +2205,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132402</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2237,6 +2312,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132405</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2339,6 +2419,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132406</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2441,6 +2526,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99906701</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2548,6 +2638,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99907368</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2645,6 +2740,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100855557</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2742,6 +2842,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100855567</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2851,6 +2956,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101910138</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2953,6 +3063,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132386</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3055,6 +3170,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132398</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3157,6 +3277,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132401</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3254,6 +3379,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100855568</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3361,6 +3491,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132382</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3468,6 +3603,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132389</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3575,6 +3715,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132395</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3723,6 +3868,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99957040</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3820,6 +3970,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100855558</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3932,6 +4087,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101909725</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4039,6 +4199,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132383</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4146,6 +4311,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132418</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4258,6 +4428,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100855577</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4364,6 +4539,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99906692</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4470,6 +4650,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99906700</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4572,6 +4757,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100855561</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4674,6 +4864,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100855575</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4792,6 +4987,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98776597</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4910,6 +5110,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98985886</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5024,6 +5229,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99677166</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5136,6 +5346,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132394</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5248,6 +5463,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132409</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5360,6 +5580,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99132411</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5482,6 +5707,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100855566</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5604,8 +5834,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100855573</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>